--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -854,7 +854,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1200%%500%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%600%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%800%%300%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -128,12 +128,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x8099ffff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -150,7 +150,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -160,7 +160,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -172,7 +172,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -182,7 +182,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -194,7 +194,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -204,7 +204,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -216,7 +216,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -226,7 +226,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -238,7 +238,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -248,7 +248,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -260,7 +260,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -270,7 +270,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -282,7 +282,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -292,7 +292,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -304,7 +304,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -314,7 +314,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -326,7 +326,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -336,7 +336,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -348,7 +348,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -358,7 +358,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -370,7 +370,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -380,7 +380,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -392,7 +392,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -402,7 +402,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -414,7 +414,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -424,7 +424,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1000%%300%%false%%0x80801a57%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -446,7 +446,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -458,12 +458,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%400%%false%%0x9980e6ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x996699ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -480,17 +480,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000073%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1a71%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%400%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0xe6e680ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>200%%300%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0xffe680ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1200%%500%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%600%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%300%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%800%%400%%false%%0xffcc99ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1200%%60%%false%%0x990000ff%%%%Dialog%%24%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%40%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0x99000000%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%true%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -453,7 +453,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -2103,7 +2103,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -2345,7 +2345,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -95,7 +95,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D146"/>
+  <dimension ref="A1:D241"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -123,12 +123,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -145,12 +145,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -167,12 +167,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -189,12 +189,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -211,12 +211,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -233,7 +233,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -255,7 +255,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -277,7 +277,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -299,7 +299,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -321,7 +321,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -343,7 +343,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -365,7 +365,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -387,7 +387,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -431,7 +431,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1289,7 +1289,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -2015,7 +2015,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -2103,7 +2103,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -2213,7 +2213,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -2345,7 +2345,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -2653,7 +2653,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -2895,7 +2895,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -3159,7 +3159,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -3269,7 +3269,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -3309,6 +3309,956 @@
           <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B163" s="2"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B166" s="2"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B167" s="2"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B179" s="2"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B181" s="2"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B182" s="2"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="2"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B183" s="2"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B189" s="2"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="2"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B190" s="2"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="2"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B191" s="2"/>
+      <c r="C191" s="2"/>
+      <c r="D191" s="2"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B192" s="2"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B193" s="2"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="2"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B194" s="2"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="2"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B195" s="2"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="2"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B196" s="2"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="2"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B197" s="2"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B198" s="2"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B199" s="2"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B200" s="2"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B201" s="2"/>
+      <c r="C201" s="2"/>
+      <c r="D201" s="2"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B202" s="2"/>
+      <c r="C202" s="2"/>
+      <c r="D202" s="2"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B203" s="2"/>
+      <c r="C203" s="2"/>
+      <c r="D203" s="2"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B204" s="2"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B205" s="2"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="2"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B206" s="2"/>
+      <c r="C206" s="2"/>
+      <c r="D206" s="2"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B207" s="2"/>
+      <c r="C207" s="2"/>
+      <c r="D207" s="2"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B208" s="2"/>
+      <c r="C208" s="2"/>
+      <c r="D208" s="2"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B209" s="2"/>
+      <c r="C209" s="2"/>
+      <c r="D209" s="2"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B210" s="2"/>
+      <c r="C210" s="2"/>
+      <c r="D210" s="2"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B211" s="2"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B212" s="2"/>
+      <c r="C212" s="2"/>
+      <c r="D212" s="2"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B213" s="2"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="2"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B214" s="2"/>
+      <c r="C214" s="2"/>
+      <c r="D214" s="2"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B216" s="2"/>
+      <c r="C216" s="2"/>
+      <c r="D216" s="2"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B217" s="2"/>
+      <c r="C217" s="2"/>
+      <c r="D217" s="2"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B218" s="2"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B219" s="2"/>
+      <c r="C219" s="2"/>
+      <c r="D219" s="2"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B221" s="2"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B222" s="2"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B223" s="2"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B224" s="2"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B225" s="2"/>
+      <c r="C225" s="2"/>
+      <c r="D225" s="2"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B226" s="2"/>
+      <c r="C226" s="2"/>
+      <c r="D226" s="2"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B227" s="2"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="2"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B228" s="2"/>
+      <c r="C228" s="2"/>
+      <c r="D228" s="2"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B229" s="2"/>
+      <c r="C229" s="2"/>
+      <c r="D229" s="2"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B230" s="2"/>
+      <c r="C230" s="2"/>
+      <c r="D230" s="2"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B231" s="2"/>
+      <c r="C231" s="2"/>
+      <c r="D231" s="2"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B232" s="2"/>
+      <c r="C232" s="2"/>
+      <c r="D232" s="2"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B233" s="2"/>
+      <c r="C233" s="2"/>
+      <c r="D233" s="2"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B234" s="2"/>
+      <c r="C234" s="2"/>
+      <c r="D234" s="2"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B235" s="2"/>
+      <c r="C235" s="2"/>
+      <c r="D235" s="2"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B236" s="2"/>
+      <c r="C236" s="2"/>
+      <c r="D236" s="2"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B237" s="2"/>
+      <c r="C237" s="2"/>
+      <c r="D237" s="2"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B238" s="2"/>
+      <c r="C238" s="2"/>
+      <c r="D238" s="2"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B239" s="2"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B240" s="2"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B241" s="2"/>
+      <c r="C241" s="2"/>
+      <c r="D241" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -123,7 +123,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -145,7 +145,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -167,7 +167,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -189,7 +189,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -211,7 +211,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -233,7 +233,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -255,7 +255,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -277,7 +277,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -299,7 +299,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -321,7 +321,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -343,7 +343,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -365,7 +365,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -387,7 +387,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -431,7 +431,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1289,7 +1289,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -2015,7 +2015,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -2103,7 +2103,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -2213,7 +2213,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -2345,7 +2345,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -2653,7 +2653,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -2895,7 +2895,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -3159,7 +3159,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -3269,7 +3269,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -150,7 +150,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -194,7 +194,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -260,7 +260,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xb36680ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -370,7 +370,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -414,7 +414,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0x804d80ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4008,7 +4008,11 @@
       </c>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
-      <c r="D216" s="2"/>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>20%%2%%300%%100%%false%%0xb31a1aff%%%%默认.ttf%%24%%false%%false%%false%%false%%居中对齐%%</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -123,7 +123,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -145,7 +145,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -167,7 +167,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -189,7 +189,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -211,7 +211,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -233,7 +233,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -255,7 +255,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -277,7 +277,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -299,7 +299,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -321,7 +321,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -343,7 +343,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -365,7 +365,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -387,12 +387,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -402,14 +402,14 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xffcc66ff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -431,7 +431,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1289,7 +1289,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%true%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -2015,7 +2015,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -2103,7 +2103,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -2213,7 +2213,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -2345,7 +2345,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -2433,12 +2433,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -2653,7 +2653,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -2895,7 +2895,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -3159,7 +3159,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -3269,7 +3269,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -123,7 +123,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -145,7 +145,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -167,7 +167,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -189,7 +189,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -211,7 +211,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -233,7 +233,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -255,7 +255,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -277,7 +277,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -299,7 +299,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -321,7 +321,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -343,7 +343,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -365,7 +365,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -387,7 +387,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -409,7 +409,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -431,7 +431,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -2015,7 +2015,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -2103,7 +2103,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -2213,7 +2213,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -2345,7 +2345,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -2653,7 +2653,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -2895,7 +2895,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -3159,7 +3159,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -3269,7 +3269,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B147" s="2"/>
@@ -3323,7 +3323,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B148" s="2"/>
@@ -3333,7 +3333,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B149" s="2"/>
@@ -3343,7 +3343,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B150" s="2"/>
@@ -3353,7 +3353,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B151" s="2"/>
@@ -3363,7 +3363,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B152" s="2"/>
@@ -3373,7 +3373,7 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B153" s="2"/>
@@ -3383,7 +3383,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B154" s="2"/>
@@ -3393,7 +3393,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B155" s="2"/>
@@ -3403,7 +3403,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B156" s="2"/>
@@ -3413,7 +3413,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B157" s="2"/>
@@ -3423,7 +3423,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B158" s="2"/>
@@ -3433,7 +3433,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B159" s="2"/>
@@ -3443,7 +3443,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B160" s="2"/>
@@ -3453,7 +3453,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B161" s="2"/>
@@ -3463,7 +3463,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B162" s="2"/>
@@ -3473,7 +3473,7 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B163" s="2"/>
@@ -3483,7 +3483,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B164" s="2"/>
@@ -3493,7 +3493,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B165" s="2"/>
@@ -3503,7 +3503,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B166" s="2"/>
@@ -3513,7 +3513,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B167" s="2"/>
@@ -3523,7 +3523,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B168" s="2"/>
@@ -3533,7 +3533,7 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B169" s="2"/>
@@ -3543,7 +3543,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B170" s="2"/>
@@ -3553,7 +3553,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B171" s="2"/>
@@ -3563,7 +3563,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B172" s="2"/>
@@ -3573,7 +3573,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B173" s="2"/>
@@ -3583,7 +3583,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B174" s="2"/>
@@ -3593,7 +3593,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B175" s="2"/>
@@ -3603,7 +3603,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B176" s="2"/>
@@ -3613,7 +3613,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B177" s="2"/>
@@ -3623,7 +3623,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B178" s="2"/>
@@ -3633,7 +3633,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B179" s="2"/>
@@ -3643,7 +3643,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B180" s="2"/>
@@ -3653,7 +3653,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B181" s="2"/>
@@ -3663,7 +3663,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B182" s="2"/>
@@ -3673,7 +3673,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B183" s="2"/>
@@ -3683,7 +3683,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B184" s="2"/>
@@ -3693,7 +3693,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B185" s="2"/>
@@ -3703,7 +3703,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B186" s="2"/>
@@ -3713,7 +3713,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B187" s="2"/>
@@ -3723,7 +3723,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B188" s="2"/>
@@ -3733,7 +3733,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B189" s="2"/>
@@ -3743,7 +3743,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B190" s="2"/>
@@ -3753,7 +3753,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B191" s="2"/>
@@ -3763,7 +3763,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B192" s="2"/>
@@ -3773,7 +3773,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B193" s="2"/>
@@ -3783,7 +3783,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B194" s="2"/>
@@ -3793,7 +3793,7 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B195" s="2"/>
@@ -3803,7 +3803,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B196" s="2"/>
@@ -3813,7 +3813,7 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B197" s="2"/>
@@ -3823,7 +3823,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B198" s="2"/>
@@ -3833,7 +3833,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B199" s="2"/>
@@ -3843,7 +3843,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B200" s="2"/>
@@ -3853,7 +3853,7 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B201" s="2"/>
@@ -3863,7 +3863,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B202" s="2"/>
@@ -3873,7 +3873,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B203" s="2"/>
@@ -3883,7 +3883,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B204" s="2"/>
@@ -3893,7 +3893,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B205" s="2"/>
@@ -3903,7 +3903,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B206" s="2"/>
@@ -3913,7 +3913,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B207" s="2"/>
@@ -3923,7 +3923,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B208" s="2"/>
@@ -3933,7 +3933,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B209" s="2"/>
@@ -3943,7 +3943,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B210" s="2"/>
@@ -3953,7 +3953,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B211" s="2"/>
@@ -3963,7 +3963,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B212" s="2"/>
@@ -3973,7 +3973,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B213" s="2"/>
@@ -3983,7 +3983,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B214" s="2"/>
@@ -3993,7 +3993,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B215" s="2"/>
@@ -4003,7 +4003,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B216" s="2"/>
@@ -4017,7 +4017,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B217" s="2"/>
@@ -4027,7 +4027,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B218" s="2"/>
@@ -4037,7 +4037,7 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B219" s="2"/>
@@ -4047,7 +4047,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="B220" s="2"/>
@@ -4057,7 +4057,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B221" s="2"/>
@@ -4067,7 +4067,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B222" s="2"/>
@@ -4077,7 +4077,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B223" s="2"/>
@@ -4087,7 +4087,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B224" s="2"/>
@@ -4097,7 +4097,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B225" s="2"/>
@@ -4107,7 +4107,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B226" s="2"/>
@@ -4117,7 +4117,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B227" s="2"/>
@@ -4127,7 +4127,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B228" s="2"/>
@@ -4137,7 +4137,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B229" s="2"/>
@@ -4147,7 +4147,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B230" s="2"/>
@@ -4157,7 +4157,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B231" s="2"/>
@@ -4167,7 +4167,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B232" s="2"/>
@@ -4177,7 +4177,7 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B233" s="2"/>
@@ -4187,7 +4187,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B234" s="2"/>
@@ -4197,17 +4197,21 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B235" s="2"/>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%200%%false%%0xffb380ff%%%%默认.ttf%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
+        </is>
+      </c>
       <c r="C235" s="2"/>
       <c r="D235" s="2"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B236" s="2"/>
@@ -4217,7 +4221,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B237" s="2"/>
@@ -4227,7 +4231,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B238" s="2"/>
@@ -4237,7 +4241,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B239" s="2"/>
@@ -4247,7 +4251,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B240" s="2"/>

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -128,7 +128,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -150,7 +150,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -172,7 +172,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -194,7 +194,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%宋体.ttc%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -238,7 +238,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -260,7 +260,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xb36680ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -282,7 +282,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -304,7 +304,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -326,7 +326,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -348,7 +348,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -392,7 +392,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -414,7 +414,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -436,7 +436,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -458,7 +458,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%12%%0%%true</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0x804d80ff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -3316,7 +3316,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B147" s="2"/>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
     </row>
@@ -3326,7 +3330,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B148" s="2"/>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
     </row>
@@ -3336,7 +3344,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B149" s="2"/>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
     </row>
@@ -3346,7 +3358,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B150" s="2"/>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
     </row>
@@ -3356,7 +3372,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B151" s="2"/>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
     </row>
@@ -3366,7 +3386,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B152" s="2"/>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
     </row>
@@ -3376,7 +3400,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B153" s="2"/>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
     </row>
@@ -3386,7 +3414,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B154" s="2"/>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
     </row>
@@ -3396,7 +3428,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B155" s="2"/>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
     </row>
@@ -3406,7 +3442,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B156" s="2"/>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
     </row>
@@ -3416,7 +3456,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B157" s="2"/>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
     </row>
@@ -3426,7 +3470,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B158" s="2"/>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
     </row>
@@ -3436,7 +3484,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B159" s="2"/>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
     </row>
@@ -3446,7 +3498,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B160" s="2"/>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
     </row>
@@ -3456,7 +3512,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B161" s="2"/>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
     </row>
@@ -3466,7 +3526,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B162" s="2"/>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
     </row>
@@ -3476,7 +3540,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B163" s="2"/>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
     </row>
@@ -3486,7 +3554,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B164" s="2"/>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
     </row>
@@ -3496,7 +3568,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B165" s="2"/>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
     </row>
@@ -3506,7 +3582,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B166" s="2"/>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
     </row>
@@ -3516,7 +3596,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B167" s="2"/>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
     </row>
@@ -3526,7 +3610,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B168" s="2"/>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
     </row>
@@ -3536,7 +3624,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B169" s="2"/>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
     </row>
@@ -3546,7 +3638,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B170" s="2"/>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
     </row>
@@ -3556,7 +3652,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B171" s="2"/>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
     </row>
@@ -3566,7 +3666,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B172" s="2"/>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
     </row>
@@ -3576,7 +3680,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B173" s="2"/>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
     </row>
@@ -3586,7 +3694,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B174" s="2"/>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
     </row>
@@ -3596,7 +3708,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B175" s="2"/>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
     </row>
@@ -3606,7 +3722,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B176" s="2"/>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
     </row>
@@ -3616,7 +3736,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B177" s="2"/>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
     </row>
@@ -3626,7 +3750,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B178" s="2"/>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
     </row>
@@ -3636,7 +3764,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B179" s="2"/>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
     </row>
@@ -3646,7 +3778,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B180" s="2"/>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
     </row>
@@ -3656,7 +3792,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B181" s="2"/>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
     </row>
@@ -3666,7 +3806,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B182" s="2"/>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
     </row>
@@ -3676,7 +3820,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B183" s="2"/>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
     </row>
@@ -3686,7 +3834,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B184" s="2"/>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
     </row>
@@ -3696,7 +3848,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B185" s="2"/>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
     </row>
@@ -3706,7 +3862,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B186" s="2"/>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
     </row>
@@ -3716,7 +3876,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B187" s="2"/>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
     </row>
@@ -3726,7 +3890,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B188" s="2"/>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
     </row>
@@ -3736,7 +3904,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B189" s="2"/>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
     </row>
@@ -3746,7 +3918,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B190" s="2"/>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
     </row>
@@ -3756,7 +3932,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B191" s="2"/>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
     </row>
@@ -3766,7 +3946,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B192" s="2"/>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
     </row>
@@ -3776,7 +3960,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B193" s="2"/>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
     </row>
@@ -3786,7 +3974,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B194" s="2"/>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
     </row>
@@ -3796,7 +3988,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B195" s="2"/>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
     </row>
@@ -3806,7 +4002,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B196" s="2"/>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
     </row>
@@ -3816,7 +4016,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B197" s="2"/>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
     </row>
@@ -3826,7 +4030,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B198" s="2"/>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
     </row>
@@ -3836,7 +4044,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B199" s="2"/>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
     </row>
@@ -3846,7 +4058,11 @@
           <t>7.1</t>
         </is>
       </c>
-      <c r="B200" s="2"/>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
     </row>
@@ -3856,7 +4072,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B201" s="2"/>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
     </row>
@@ -3866,7 +4086,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B202" s="2"/>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
     </row>
@@ -3876,7 +4100,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B203" s="2"/>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
     </row>
@@ -3886,7 +4114,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B204" s="2"/>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
     </row>
@@ -3896,7 +4128,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B205" s="2"/>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
     </row>
@@ -3906,7 +4142,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B206" s="2"/>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
     </row>
@@ -3916,7 +4156,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B207" s="2"/>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
     </row>
@@ -3926,7 +4170,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B208" s="2"/>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
     </row>
@@ -3936,7 +4184,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B209" s="2"/>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
     </row>
@@ -3946,7 +4198,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B210" s="2"/>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
     </row>
@@ -3956,7 +4212,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B211" s="2"/>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
     </row>
@@ -3966,7 +4226,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B212" s="2"/>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
     </row>
@@ -3976,7 +4240,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B213" s="2"/>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
     </row>
@@ -3986,7 +4254,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B214" s="2"/>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
     </row>
@@ -3996,7 +4268,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B215" s="2"/>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
     </row>
@@ -4006,7 +4282,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B216" s="2"/>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C216" s="2"/>
       <c r="D216" s="2" t="inlineStr">
         <is>
@@ -4020,7 +4300,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B217" s="2"/>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C217" s="2"/>
       <c r="D217" s="2"/>
     </row>
@@ -4030,7 +4314,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B218" s="2"/>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
     </row>
@@ -4040,7 +4328,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B219" s="2"/>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C219" s="2"/>
       <c r="D219" s="2"/>
     </row>
@@ -4050,7 +4342,11 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="B220" s="2"/>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
     </row>
@@ -4060,7 +4356,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B221" s="2"/>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>
     </row>
@@ -4070,7 +4370,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B222" s="2"/>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
     </row>
@@ -4080,7 +4384,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B223" s="2"/>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C223" s="2"/>
       <c r="D223" s="2"/>
     </row>
@@ -4090,7 +4398,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B224" s="2"/>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C224" s="2"/>
       <c r="D224" s="2"/>
     </row>
@@ -4100,7 +4412,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B225" s="2"/>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C225" s="2"/>
       <c r="D225" s="2"/>
     </row>
@@ -4110,7 +4426,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B226" s="2"/>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C226" s="2"/>
       <c r="D226" s="2"/>
     </row>
@@ -4120,7 +4440,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B227" s="2"/>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C227" s="2"/>
       <c r="D227" s="2"/>
     </row>
@@ -4130,7 +4454,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B228" s="2"/>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
     </row>
@@ -4140,7 +4468,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B229" s="2"/>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
     </row>
@@ -4150,7 +4482,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B230" s="2"/>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
     </row>
@@ -4160,7 +4496,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B231" s="2"/>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C231" s="2"/>
       <c r="D231" s="2"/>
     </row>
@@ -4170,7 +4510,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B232" s="2"/>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C232" s="2"/>
       <c r="D232" s="2"/>
     </row>
@@ -4180,7 +4524,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B233" s="2"/>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C233" s="2"/>
       <c r="D233" s="2"/>
     </row>
@@ -4190,7 +4538,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B234" s="2"/>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C234" s="2"/>
       <c r="D234" s="2"/>
     </row>
@@ -4202,7 +4554,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%200%%false%%0xffb380ff%%%%默认.ttf%%30%%false%%false%%false%%false%%左对齐%%10%%0%%false</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C235" s="2"/>
@@ -4214,7 +4566,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B236" s="2"/>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C236" s="2"/>
       <c r="D236" s="2"/>
     </row>
@@ -4224,7 +4580,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B237" s="2"/>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C237" s="2"/>
       <c r="D237" s="2"/>
     </row>
@@ -4234,7 +4594,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B238" s="2"/>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C238" s="2"/>
       <c r="D238" s="2"/>
     </row>
@@ -4244,7 +4608,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B239" s="2"/>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
     </row>
@@ -4254,7 +4622,11 @@
           <t>7.3</t>
         </is>
       </c>
-      <c r="B240" s="2"/>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C240" s="2"/>
       <c r="D240" s="2"/>
     </row>
@@ -4264,7 +4636,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B241" s="2"/>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
     </row>

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -771,7 +771,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%2</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -859,12 +859,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0xffffffff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xffffffff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xffffffff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xffffffff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%2</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%80%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4245,7 +4245,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C213" s="2"/>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xffccccff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D213" s="2"/>
     </row>
     <row r="214">
@@ -4417,7 +4421,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C225" s="2"/>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0x8066ccff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D225" s="2"/>
     </row>
     <row r="226">
@@ -4445,7 +4453,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C227" s="2"/>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xffe6ccff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%3</t>
+        </is>
+      </c>
       <c r="D227" s="2"/>
     </row>
     <row r="228">

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -128,7 +128,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%MS UI Gothic%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -138,7 +138,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%Colonna MT%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -150,7 +150,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -160,7 +160,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%Berlin Sans FB%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -380,7 +380,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xffffffff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -436,7 +436,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Bernard MT Condensed%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xffff66ff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%微软雅黑%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%100%%1400%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%650%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3416,11 +3416,19 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
-        </is>
-      </c>
-      <c r="C154" s="2"/>
-      <c r="D154" s="2"/>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%默认.ttf%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0x9980e6ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>2%%2%%300%%100%%false%%0xb31a1aff%%%%默认.ttf%%24%%false%%true%%false%%false%%居中对齐%%10</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -3630,7 +3638,11 @@
         </is>
       </c>
       <c r="C169" s="2"/>
-      <c r="D169" s="2"/>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>2%%2%%300%%100%%false%%0xb31a1aff%%%%默认.ttf%%24%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -128,17 +128,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%MS UI Gothic%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%Colonna MT%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%Agency FB%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -155,12 +155,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%Berlin Sans FB%%24%%false%%false%%false%%false%%居中对齐%%10</t>
+          <t>2%%60%%300%%80%%false%%0xb31a1aff%%D:\Users\Administrator\Desktop\竞赛软件(2)\竞赛软件\资源\图片\标题.png%%华文中宋.TTF%%24%%false%%false%%false%%false%%居中对齐%%10</t>
         </is>
       </c>
     </row>
@@ -172,12 +172,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -194,12 +194,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%800%%false%%0xcccc66ff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -238,12 +238,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -260,12 +260,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -282,12 +282,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -304,12 +304,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -348,12 +348,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -370,12 +370,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -392,12 +392,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -414,12 +414,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -436,12 +436,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Bernard MT Condensed%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -458,12 +458,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -480,12 +480,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -502,12 +502,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -568,12 +568,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -590,12 +590,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -612,12 +612,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -634,12 +634,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -656,12 +656,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -810,12 +810,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0xffffffff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0xffffffff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%12%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%12%%0%%true</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%2</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%2</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%100%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>200%%100%%1400%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%100%%1400%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>200%%650%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%650%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%2</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%2</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%true%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%true%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -2196,12 +2196,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%80%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%80%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -2768,12 +2768,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Dialog%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x990000ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C147" s="2"/>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C148" s="2"/>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C149" s="2"/>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C150" s="2"/>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C151" s="2"/>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C152" s="2"/>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C153" s="2"/>
@@ -3416,12 +3416,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%默认.ttf%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x9980e6ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x9980e6ff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C155" s="2"/>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C156" s="2"/>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C157" s="2"/>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C158" s="2"/>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C159" s="2"/>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C160" s="2"/>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C161" s="2"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C162" s="2"/>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C163" s="2"/>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C164" s="2"/>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C165" s="2"/>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C166" s="2"/>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C167" s="2"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C168" s="2"/>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C169" s="2"/>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C170" s="2"/>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C171" s="2"/>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C172" s="2"/>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C173" s="2"/>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C174" s="2"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C175" s="2"/>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C176" s="2"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C177" s="2"/>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C178" s="2"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C179" s="2"/>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C180" s="2"/>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C181" s="2"/>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C182" s="2"/>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C183" s="2"/>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C184" s="2"/>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C185" s="2"/>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C186" s="2"/>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C187" s="2"/>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C188" s="2"/>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C189" s="2"/>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C190" s="2"/>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C191" s="2"/>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C192" s="2"/>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C193" s="2"/>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C194" s="2"/>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C195" s="2"/>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C196" s="2"/>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C197" s="2"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C198" s="2"/>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C199" s="2"/>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C200" s="2"/>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C201" s="2"/>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C202" s="2"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C203" s="2"/>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C204" s="2"/>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C205" s="2"/>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C206" s="2"/>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C207" s="2"/>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C208" s="2"/>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C209" s="2"/>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C210" s="2"/>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C211" s="2"/>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C212" s="2"/>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0xffccccff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0xffccccff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D213" s="2"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C214" s="2"/>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C215" s="2"/>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C216" s="2"/>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C217" s="2"/>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C218" s="2"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C219" s="2"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C220" s="2"/>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C221" s="2"/>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C222" s="2"/>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C223" s="2"/>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C224" s="2"/>
@@ -4430,12 +4430,12 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0x8066ccff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+          <t>200%%700%%1550%%60%%false%%0x8066ccff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%0</t>
         </is>
       </c>
       <c r="D225" s="2"/>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C226" s="2"/>
@@ -4462,12 +4462,12 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>200%%700%%1550%%60%%false%%0xffe6ccff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%3</t>
+          <t>200%%700%%1550%%60%%false%%0xffe6ccff%%%%Arial%%36%%false%%false%%false%%false%%居中对齐%%3</t>
         </is>
       </c>
       <c r="D227" s="2"/>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C228" s="2"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C229" s="2"/>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C230" s="2"/>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C231" s="2"/>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C232" s="2"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C233" s="2"/>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C234" s="2"/>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C235" s="2"/>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C236" s="2"/>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C237" s="2"/>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C238" s="2"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C239" s="2"/>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C240" s="2"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%Microsoft YaHei%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
+          <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
       <c r="C241" s="2"/>

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -3809,7 +3809,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C181" s="2"/>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D181" s="2"/>
     </row>
     <row r="182">
@@ -3823,7 +3827,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C182" s="2"/>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D182" s="2"/>
     </row>
     <row r="183">
@@ -3837,7 +3845,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C183" s="2"/>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D183" s="2"/>
     </row>
     <row r="184">
@@ -3851,7 +3863,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C184" s="2"/>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D184" s="2"/>
     </row>
     <row r="185">
@@ -3865,7 +3881,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C185" s="2"/>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D185" s="2"/>
     </row>
     <row r="186">
@@ -3879,7 +3899,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C186" s="2"/>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D186" s="2"/>
     </row>
     <row r="187">
@@ -3893,7 +3917,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C187" s="2"/>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D187" s="2"/>
     </row>
     <row r="188">
@@ -3907,7 +3935,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C188" s="2"/>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D188" s="2"/>
     </row>
     <row r="189">
@@ -3921,7 +3953,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C189" s="2"/>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D189" s="2"/>
     </row>
     <row r="190">
@@ -3935,7 +3971,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C190" s="2"/>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D190" s="2"/>
     </row>
     <row r="191">
@@ -3949,7 +3989,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C191" s="2"/>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D191" s="2"/>
     </row>
     <row r="192">
@@ -3963,7 +4007,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C192" s="2"/>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D192" s="2"/>
     </row>
     <row r="193">
@@ -3977,7 +4025,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C193" s="2"/>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D193" s="2"/>
     </row>
     <row r="194">
@@ -3991,7 +4043,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C194" s="2"/>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D194" s="2"/>
     </row>
     <row r="195">
@@ -4005,7 +4061,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C195" s="2"/>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D195" s="2"/>
     </row>
     <row r="196">
@@ -4019,7 +4079,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C196" s="2"/>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D196" s="2"/>
     </row>
     <row r="197">
@@ -4033,7 +4097,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C197" s="2"/>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D197" s="2"/>
     </row>
     <row r="198">
@@ -4047,7 +4115,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C198" s="2"/>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D198" s="2"/>
     </row>
     <row r="199">
@@ -4061,7 +4133,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C199" s="2"/>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D199" s="2"/>
     </row>
     <row r="200">
@@ -4075,7 +4151,11 @@
           <t>200%%200%%1550%%700%%false%%0xffffffff%%%%方正舒体%%30%%false%%false%%false%%false%%左对齐%%10%%0%%true</t>
         </is>
       </c>
-      <c r="C200" s="2"/>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>200%%700%%1550%%60%%false%%0xcc8099ff%%%%默认.ttf%%36%%false%%false%%false%%false%%居中对齐%%0</t>
+        </is>
+      </c>
       <c r="D200" s="2"/>
     </row>
     <row r="201">

--- a/fx-server/资源/样式/样式.xlsx
+++ b/fx-server/资源/样式/样式.xlsx
@@ -4449,7 +4449,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -4505,7 +4505,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -4555,7 +4555,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -4583,7 +4583,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -4611,7 +4611,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -4639,7 +4639,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -4709,7 +4709,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -4723,7 +4723,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
